--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348734</v>
+        <v>120348745</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558164</v>
+        <v>558319</v>
       </c>
       <c r="R2" t="n">
-        <v>6992800</v>
+        <v>6992534</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348735</v>
+        <v>120348716</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558167</v>
+        <v>558377</v>
       </c>
       <c r="R3" t="n">
-        <v>6992805</v>
+        <v>6992894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348721</v>
+        <v>120348723</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558410</v>
+        <v>558226</v>
       </c>
       <c r="R4" t="n">
-        <v>6992910</v>
+        <v>6992680</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348741</v>
+        <v>120348721</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558382</v>
+        <v>558410</v>
       </c>
       <c r="R5" t="n">
-        <v>6992903</v>
+        <v>6992910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348722</v>
+        <v>120348725</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558400</v>
+        <v>558215</v>
       </c>
       <c r="R6" t="n">
-        <v>6992530</v>
+        <v>6992721</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348737</v>
+        <v>120348738</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558163</v>
+        <v>558160</v>
       </c>
       <c r="R7" t="n">
-        <v>6992824</v>
+        <v>6992833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348736</v>
+        <v>120348719</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558159</v>
+        <v>558395</v>
       </c>
       <c r="R8" t="n">
-        <v>6992813</v>
+        <v>6992947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348724</v>
+        <v>120348714</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558220</v>
+        <v>558187</v>
       </c>
       <c r="R9" t="n">
-        <v>6992703</v>
+        <v>6992755</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348717</v>
+        <v>120348737</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558383</v>
+        <v>558163</v>
       </c>
       <c r="R10" t="n">
-        <v>6992932</v>
+        <v>6992824</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348738</v>
+        <v>120348730</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558160</v>
+        <v>558182</v>
       </c>
       <c r="R11" t="n">
-        <v>6992833</v>
+        <v>6992774</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348745</v>
+        <v>120348742</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558319</v>
+        <v>558360</v>
       </c>
       <c r="R12" t="n">
-        <v>6992534</v>
+        <v>6992917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348716</v>
+        <v>120348726</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558377</v>
+        <v>558200</v>
       </c>
       <c r="R13" t="n">
-        <v>6992894</v>
+        <v>6992737</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348715</v>
+        <v>120348729</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558347</v>
+        <v>558183</v>
       </c>
       <c r="R14" t="n">
-        <v>6992956</v>
+        <v>6992756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +1995,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348731</v>
+        <v>120348713</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558175</v>
+        <v>558254</v>
       </c>
       <c r="R15" t="n">
-        <v>6992771</v>
+        <v>6992648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348726</v>
+        <v>120348739</v>
       </c>
       <c r="B16" t="n">
         <v>79623</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558200</v>
+        <v>558156</v>
       </c>
       <c r="R16" t="n">
-        <v>6992737</v>
+        <v>6992824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348714</v>
+        <v>120348731</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558187</v>
+        <v>558175</v>
       </c>
       <c r="R17" t="n">
-        <v>6992755</v>
+        <v>6992771</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348723</v>
+        <v>120348717</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558226</v>
+        <v>558383</v>
       </c>
       <c r="R18" t="n">
-        <v>6992680</v>
+        <v>6992932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2408,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348740</v>
+        <v>120348744</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,25 +2451,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558150</v>
+        <v>558367</v>
       </c>
       <c r="R19" t="n">
-        <v>6992821</v>
+        <v>6992910</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348713</v>
+        <v>120348724</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558254</v>
+        <v>558220</v>
       </c>
       <c r="R20" t="n">
-        <v>6992648</v>
+        <v>6992703</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,11 +2617,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2648,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348744</v>
+        <v>120348741</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2660,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558367</v>
+        <v>558382</v>
       </c>
       <c r="R21" t="n">
-        <v>6992910</v>
+        <v>6992903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348720</v>
+        <v>120348734</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558403</v>
+        <v>558164</v>
       </c>
       <c r="R22" t="n">
-        <v>6992930</v>
+        <v>6992800</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2857,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120348719</v>
+        <v>120348728</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558395</v>
+        <v>558195</v>
       </c>
       <c r="R23" t="n">
-        <v>6992947</v>
+        <v>6992750</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348732</v>
+        <v>120348718</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558177</v>
+        <v>558397</v>
       </c>
       <c r="R24" t="n">
-        <v>6992782</v>
+        <v>6992950</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3040,6 +3025,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3066,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348718</v>
+        <v>120348720</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3106,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558397</v>
+        <v>558403</v>
       </c>
       <c r="R25" t="n">
-        <v>6992950</v>
+        <v>6992930</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3173,7 +3163,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348729</v>
+        <v>120348736</v>
       </c>
       <c r="B26" t="n">
         <v>79623</v>
@@ -3213,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558183</v>
+        <v>558159</v>
       </c>
       <c r="R26" t="n">
-        <v>6992756</v>
+        <v>6992813</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120348742</v>
+        <v>120348735</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3287,25 +3277,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558360</v>
+        <v>558167</v>
       </c>
       <c r="R27" t="n">
-        <v>6992917</v>
+        <v>6992805</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3377,7 +3367,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348739</v>
+        <v>120348740</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3417,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558156</v>
+        <v>558150</v>
       </c>
       <c r="R28" t="n">
-        <v>6992824</v>
+        <v>6992821</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348728</v>
+        <v>120348715</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,21 +3485,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558195</v>
+        <v>558347</v>
       </c>
       <c r="R29" t="n">
-        <v>6992750</v>
+        <v>6992956</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3555,6 +3545,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3581,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348730</v>
+        <v>120348722</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,21 +3592,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558182</v>
+        <v>558400</v>
       </c>
       <c r="R30" t="n">
-        <v>6992774</v>
+        <v>6992530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,6 +3652,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348725</v>
+        <v>120348732</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558215</v>
+        <v>558177</v>
       </c>
       <c r="R31" t="n">
-        <v>6992721</v>
+        <v>6992782</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348745</v>
+        <v>120348732</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558319</v>
+        <v>558177</v>
       </c>
       <c r="R2" t="n">
-        <v>6992534</v>
+        <v>6992782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348716</v>
+        <v>120348718</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558377</v>
+        <v>558397</v>
       </c>
       <c r="R3" t="n">
-        <v>6992894</v>
+        <v>6992950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348723</v>
+        <v>120348717</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558226</v>
+        <v>558383</v>
       </c>
       <c r="R4" t="n">
-        <v>6992680</v>
+        <v>6992932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348721</v>
+        <v>120348739</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558410</v>
+        <v>558156</v>
       </c>
       <c r="R5" t="n">
-        <v>6992910</v>
+        <v>6992824</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348725</v>
+        <v>120348740</v>
       </c>
       <c r="B6" t="n">
         <v>79623</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558215</v>
+        <v>558150</v>
       </c>
       <c r="R6" t="n">
-        <v>6992721</v>
+        <v>6992821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348738</v>
+        <v>120348728</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558160</v>
+        <v>558195</v>
       </c>
       <c r="R7" t="n">
-        <v>6992833</v>
+        <v>6992750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348719</v>
+        <v>120348716</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558395</v>
+        <v>558377</v>
       </c>
       <c r="R8" t="n">
-        <v>6992947</v>
+        <v>6992894</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348714</v>
+        <v>120348744</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558187</v>
+        <v>558367</v>
       </c>
       <c r="R9" t="n">
-        <v>6992755</v>
+        <v>6992910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348737</v>
+        <v>120348726</v>
       </c>
       <c r="B10" t="n">
         <v>79623</v>
@@ -1551,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558163</v>
+        <v>558200</v>
       </c>
       <c r="R10" t="n">
-        <v>6992824</v>
+        <v>6992737</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348730</v>
+        <v>120348731</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558182</v>
+        <v>558175</v>
       </c>
       <c r="R11" t="n">
-        <v>6992774</v>
+        <v>6992771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348742</v>
+        <v>120348720</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558360</v>
+        <v>558403</v>
       </c>
       <c r="R12" t="n">
-        <v>6992917</v>
+        <v>6992930</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348726</v>
+        <v>120348730</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558200</v>
+        <v>558182</v>
       </c>
       <c r="R13" t="n">
-        <v>6992737</v>
+        <v>6992774</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348729</v>
+        <v>120348713</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558183</v>
+        <v>558254</v>
       </c>
       <c r="R14" t="n">
-        <v>6992756</v>
+        <v>6992648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,6 +1995,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348713</v>
+        <v>120348741</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558254</v>
+        <v>558382</v>
       </c>
       <c r="R15" t="n">
-        <v>6992648</v>
+        <v>6992903</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2102,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348739</v>
+        <v>120348745</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558156</v>
+        <v>558319</v>
       </c>
       <c r="R16" t="n">
-        <v>6992824</v>
+        <v>6992534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348731</v>
+        <v>120348734</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558175</v>
+        <v>558164</v>
       </c>
       <c r="R17" t="n">
-        <v>6992771</v>
+        <v>6992800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348717</v>
+        <v>120348738</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558383</v>
+        <v>558160</v>
       </c>
       <c r="R18" t="n">
-        <v>6992932</v>
+        <v>6992833</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,11 +2408,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348744</v>
+        <v>120348729</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558367</v>
+        <v>558183</v>
       </c>
       <c r="R19" t="n">
-        <v>6992910</v>
+        <v>6992756</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348741</v>
+        <v>120348721</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558382</v>
+        <v>558410</v>
       </c>
       <c r="R21" t="n">
-        <v>6992903</v>
+        <v>6992910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,6 +2714,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348734</v>
+        <v>120348715</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558164</v>
+        <v>558347</v>
       </c>
       <c r="R22" t="n">
-        <v>6992800</v>
+        <v>6992956</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,7 +2852,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120348728</v>
+        <v>120348736</v>
       </c>
       <c r="B23" t="n">
         <v>79623</v>
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558195</v>
+        <v>558159</v>
       </c>
       <c r="R23" t="n">
-        <v>6992750</v>
+        <v>6992813</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348718</v>
+        <v>120348742</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2961,25 +2966,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558397</v>
+        <v>558360</v>
       </c>
       <c r="R24" t="n">
-        <v>6992950</v>
+        <v>6992917</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,11 +3030,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348720</v>
+        <v>120348722</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558403</v>
+        <v>558400</v>
       </c>
       <c r="R25" t="n">
-        <v>6992930</v>
+        <v>6992530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348736</v>
+        <v>120348714</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558159</v>
+        <v>558187</v>
       </c>
       <c r="R26" t="n">
-        <v>6992813</v>
+        <v>6992755</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,6 +3239,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3367,7 +3372,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348740</v>
+        <v>120348723</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3407,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558150</v>
+        <v>558226</v>
       </c>
       <c r="R28" t="n">
-        <v>6992821</v>
+        <v>6992680</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,10 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348715</v>
+        <v>120348725</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3485,21 +3490,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558347</v>
+        <v>558215</v>
       </c>
       <c r="R29" t="n">
-        <v>6992956</v>
+        <v>6992721</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,11 +3550,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348722</v>
+        <v>120348737</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3592,21 +3592,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558400</v>
+        <v>558163</v>
       </c>
       <c r="R30" t="n">
-        <v>6992530</v>
+        <v>6992824</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,11 +3652,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,10 +3678,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348732</v>
+        <v>120348719</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,21 +3694,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3723,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558177</v>
+        <v>558395</v>
       </c>
       <c r="R31" t="n">
-        <v>6992782</v>
+        <v>6992947</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,6 +3754,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348734</v>
+        <v>120348721</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558164</v>
+        <v>558410</v>
       </c>
       <c r="R17" t="n">
-        <v>6992800</v>
+        <v>6992910</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2306,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348738</v>
+        <v>120348715</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558160</v>
+        <v>558347</v>
       </c>
       <c r="R18" t="n">
-        <v>6992833</v>
+        <v>6992956</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,6 +2413,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,7 +2444,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348729</v>
+        <v>120348734</v>
       </c>
       <c r="B19" t="n">
         <v>79623</v>
@@ -2474,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558183</v>
+        <v>558164</v>
       </c>
       <c r="R19" t="n">
-        <v>6992756</v>
+        <v>6992800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2546,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348724</v>
+        <v>120348738</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -2576,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558220</v>
+        <v>558160</v>
       </c>
       <c r="R20" t="n">
-        <v>6992703</v>
+        <v>6992833</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348721</v>
+        <v>120348729</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558410</v>
+        <v>558183</v>
       </c>
       <c r="R21" t="n">
-        <v>6992910</v>
+        <v>6992756</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2714,11 +2724,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348715</v>
+        <v>120348724</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2766,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558347</v>
+        <v>558220</v>
       </c>
       <c r="R22" t="n">
-        <v>6992956</v>
+        <v>6992703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2826,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348737</v>
+        <v>120348719</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3592,21 +3592,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558163</v>
+        <v>558395</v>
       </c>
       <c r="R30" t="n">
-        <v>6992824</v>
+        <v>6992947</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,6 +3652,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3678,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348719</v>
+        <v>120348737</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3694,21 +3699,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558395</v>
+        <v>558163</v>
       </c>
       <c r="R31" t="n">
-        <v>6992947</v>
+        <v>6992824</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,11 +3759,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348732</v>
+        <v>120348717</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558177</v>
+        <v>558383</v>
       </c>
       <c r="R2" t="n">
-        <v>6992782</v>
+        <v>6992932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348718</v>
+        <v>120348714</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558397</v>
+        <v>558187</v>
       </c>
       <c r="R3" t="n">
-        <v>6992950</v>
+        <v>6992755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348717</v>
+        <v>120348738</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558383</v>
+        <v>558160</v>
       </c>
       <c r="R4" t="n">
-        <v>6992932</v>
+        <v>6992833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348740</v>
+        <v>120348728</v>
       </c>
       <c r="B6" t="n">
         <v>79623</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558150</v>
+        <v>558195</v>
       </c>
       <c r="R6" t="n">
-        <v>6992821</v>
+        <v>6992750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348728</v>
+        <v>120348719</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558195</v>
+        <v>558395</v>
       </c>
       <c r="R7" t="n">
-        <v>6992750</v>
+        <v>6992947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348716</v>
+        <v>120348721</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558377</v>
+        <v>558410</v>
       </c>
       <c r="R8" t="n">
-        <v>6992894</v>
+        <v>6992910</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348744</v>
+        <v>120348735</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558367</v>
+        <v>558167</v>
       </c>
       <c r="R9" t="n">
-        <v>6992910</v>
+        <v>6992805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348731</v>
+        <v>120348713</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558175</v>
+        <v>558254</v>
       </c>
       <c r="R11" t="n">
-        <v>6992771</v>
+        <v>6992648</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348730</v>
+        <v>120348723</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -1857,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558182</v>
+        <v>558226</v>
       </c>
       <c r="R13" t="n">
-        <v>6992774</v>
+        <v>6992680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348713</v>
+        <v>120348745</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558254</v>
+        <v>558319</v>
       </c>
       <c r="R14" t="n">
-        <v>6992648</v>
+        <v>6992534</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348741</v>
+        <v>120348731</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2066,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558382</v>
+        <v>558175</v>
       </c>
       <c r="R15" t="n">
-        <v>6992903</v>
+        <v>6992771</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348745</v>
+        <v>120348740</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558319</v>
+        <v>558150</v>
       </c>
       <c r="R16" t="n">
-        <v>6992534</v>
+        <v>6992821</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348721</v>
+        <v>120348725</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2251,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558410</v>
+        <v>558215</v>
       </c>
       <c r="R17" t="n">
-        <v>6992910</v>
+        <v>6992721</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,11 +2311,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348715</v>
+        <v>120348724</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558347</v>
+        <v>558220</v>
       </c>
       <c r="R18" t="n">
-        <v>6992956</v>
+        <v>6992703</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348734</v>
+        <v>120348716</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558164</v>
+        <v>558377</v>
       </c>
       <c r="R19" t="n">
-        <v>6992800</v>
+        <v>6992894</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,6 +2515,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,7 +2546,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348738</v>
+        <v>120348732</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558160</v>
+        <v>558177</v>
       </c>
       <c r="R20" t="n">
-        <v>6992833</v>
+        <v>6992782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348729</v>
+        <v>120348742</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2660,25 +2660,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558183</v>
+        <v>558360</v>
       </c>
       <c r="R21" t="n">
-        <v>6992756</v>
+        <v>6992917</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348724</v>
+        <v>120348741</v>
       </c>
       <c r="B22" t="n">
         <v>79623</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558220</v>
+        <v>558382</v>
       </c>
       <c r="R22" t="n">
-        <v>6992703</v>
+        <v>6992903</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348742</v>
+        <v>120348722</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2966,25 +2966,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558360</v>
+        <v>558400</v>
       </c>
       <c r="R24" t="n">
-        <v>6992917</v>
+        <v>6992530</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348722</v>
+        <v>120348734</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558400</v>
+        <v>558164</v>
       </c>
       <c r="R25" t="n">
-        <v>6992530</v>
+        <v>6992800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,11 +3137,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348714</v>
+        <v>120348729</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558187</v>
+        <v>558183</v>
       </c>
       <c r="R26" t="n">
-        <v>6992755</v>
+        <v>6992756</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,11 +3239,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3270,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120348735</v>
+        <v>120348715</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,21 +3281,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558167</v>
+        <v>558347</v>
       </c>
       <c r="R27" t="n">
-        <v>6992805</v>
+        <v>6992956</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,6 +3341,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348723</v>
+        <v>120348744</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3384,25 +3384,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558226</v>
+        <v>558367</v>
       </c>
       <c r="R28" t="n">
-        <v>6992680</v>
+        <v>6992910</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348725</v>
+        <v>120348737</v>
       </c>
       <c r="B29" t="n">
         <v>79623</v>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558215</v>
+        <v>558163</v>
       </c>
       <c r="R29" t="n">
-        <v>6992721</v>
+        <v>6992824</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348719</v>
+        <v>120348730</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3592,21 +3592,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558395</v>
+        <v>558182</v>
       </c>
       <c r="R30" t="n">
-        <v>6992947</v>
+        <v>6992774</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,11 +3652,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,10 +3678,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348737</v>
+        <v>120348718</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,21 +3694,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3723,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558163</v>
+        <v>558397</v>
       </c>
       <c r="R31" t="n">
-        <v>6992824</v>
+        <v>6992950</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,6 +3754,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348721</v>
+        <v>120348735</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558410</v>
+        <v>558167</v>
       </c>
       <c r="R8" t="n">
-        <v>6992910</v>
+        <v>6992805</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348735</v>
+        <v>120348721</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558167</v>
+        <v>558410</v>
       </c>
       <c r="R9" t="n">
-        <v>6992805</v>
+        <v>6992910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2439,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348716</v>
+        <v>120348732</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558377</v>
+        <v>558177</v>
       </c>
       <c r="R19" t="n">
-        <v>6992894</v>
+        <v>6992782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348732</v>
+        <v>120348716</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558177</v>
+        <v>558377</v>
       </c>
       <c r="R20" t="n">
-        <v>6992782</v>
+        <v>6992894</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,6 +2617,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348730</v>
+        <v>120348718</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3592,21 +3592,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558182</v>
+        <v>558397</v>
       </c>
       <c r="R30" t="n">
-        <v>6992774</v>
+        <v>6992950</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,6 +3652,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3678,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348718</v>
+        <v>120348730</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3694,21 +3699,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558397</v>
+        <v>558182</v>
       </c>
       <c r="R31" t="n">
-        <v>6992950</v>
+        <v>6992774</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,11 +3759,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348717</v>
+        <v>120348737</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558383</v>
+        <v>558163</v>
       </c>
       <c r="R2" t="n">
-        <v>6992932</v>
+        <v>6992824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348714</v>
+        <v>120348728</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558187</v>
+        <v>558195</v>
       </c>
       <c r="R3" t="n">
-        <v>6992755</v>
+        <v>6992750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348738</v>
+        <v>120348718</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558160</v>
+        <v>558397</v>
       </c>
       <c r="R4" t="n">
-        <v>6992833</v>
+        <v>6992950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348739</v>
+        <v>120348731</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558156</v>
+        <v>558175</v>
       </c>
       <c r="R5" t="n">
-        <v>6992824</v>
+        <v>6992771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348728</v>
+        <v>120348739</v>
       </c>
       <c r="B6" t="n">
         <v>79623</v>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558195</v>
+        <v>558156</v>
       </c>
       <c r="R6" t="n">
-        <v>6992750</v>
+        <v>6992824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348719</v>
+        <v>120348738</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558395</v>
+        <v>558160</v>
       </c>
       <c r="R7" t="n">
-        <v>6992947</v>
+        <v>6992833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348735</v>
+        <v>120348740</v>
       </c>
       <c r="B8" t="n">
         <v>79623</v>
@@ -1342,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558167</v>
+        <v>558150</v>
       </c>
       <c r="R8" t="n">
-        <v>6992805</v>
+        <v>6992821</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348726</v>
+        <v>120348715</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558200</v>
+        <v>558347</v>
       </c>
       <c r="R10" t="n">
-        <v>6992737</v>
+        <v>6992956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348713</v>
+        <v>120348725</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558254</v>
+        <v>558215</v>
       </c>
       <c r="R11" t="n">
-        <v>6992648</v>
+        <v>6992721</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1684,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348720</v>
+        <v>120348729</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558403</v>
+        <v>558183</v>
       </c>
       <c r="R12" t="n">
-        <v>6992930</v>
+        <v>6992756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348723</v>
+        <v>120348736</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -1867,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558226</v>
+        <v>558159</v>
       </c>
       <c r="R13" t="n">
-        <v>6992680</v>
+        <v>6992813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348745</v>
+        <v>120348722</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558319</v>
+        <v>558400</v>
       </c>
       <c r="R14" t="n">
-        <v>6992534</v>
+        <v>6992530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348731</v>
+        <v>120348724</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2071,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558175</v>
+        <v>558220</v>
       </c>
       <c r="R15" t="n">
-        <v>6992771</v>
+        <v>6992703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348740</v>
+        <v>120348742</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558150</v>
+        <v>558360</v>
       </c>
       <c r="R16" t="n">
-        <v>6992821</v>
+        <v>6992917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348725</v>
+        <v>120348745</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558215</v>
+        <v>558319</v>
       </c>
       <c r="R17" t="n">
-        <v>6992721</v>
+        <v>6992534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348724</v>
+        <v>120348717</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558220</v>
+        <v>558383</v>
       </c>
       <c r="R18" t="n">
-        <v>6992703</v>
+        <v>6992932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2434,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348732</v>
+        <v>120348735</v>
       </c>
       <c r="B19" t="n">
         <v>79623</v>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558177</v>
+        <v>558167</v>
       </c>
       <c r="R19" t="n">
-        <v>6992782</v>
+        <v>6992805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348716</v>
+        <v>120348730</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558377</v>
+        <v>558182</v>
       </c>
       <c r="R20" t="n">
-        <v>6992894</v>
+        <v>6992774</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,11 +2612,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2648,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348742</v>
+        <v>120348726</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2660,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558360</v>
+        <v>558200</v>
       </c>
       <c r="R21" t="n">
-        <v>6992917</v>
+        <v>6992737</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348741</v>
+        <v>120348716</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558382</v>
+        <v>558377</v>
       </c>
       <c r="R22" t="n">
-        <v>6992903</v>
+        <v>6992894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,6 +2816,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120348736</v>
+        <v>120348744</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2864,25 +2859,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558159</v>
+        <v>558367</v>
       </c>
       <c r="R23" t="n">
-        <v>6992813</v>
+        <v>6992910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348722</v>
+        <v>120348741</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2970,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558400</v>
+        <v>558382</v>
       </c>
       <c r="R24" t="n">
-        <v>6992530</v>
+        <v>6992903</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,11 +3025,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348734</v>
+        <v>120348719</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558164</v>
+        <v>558395</v>
       </c>
       <c r="R25" t="n">
-        <v>6992800</v>
+        <v>6992947</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3137,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348729</v>
+        <v>120348714</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558183</v>
+        <v>558187</v>
       </c>
       <c r="R26" t="n">
-        <v>6992756</v>
+        <v>6992755</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,6 +3234,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3265,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120348715</v>
+        <v>120348732</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3281,21 +3281,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558347</v>
+        <v>558177</v>
       </c>
       <c r="R27" t="n">
-        <v>6992956</v>
+        <v>6992782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,11 +3341,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,10 +3367,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348744</v>
+        <v>120348720</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3384,25 +3379,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3412,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558367</v>
+        <v>558403</v>
       </c>
       <c r="R28" t="n">
-        <v>6992910</v>
+        <v>6992930</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,6 +3443,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3474,7 +3474,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348737</v>
+        <v>120348734</v>
       </c>
       <c r="B29" t="n">
         <v>79623</v>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558163</v>
+        <v>558164</v>
       </c>
       <c r="R29" t="n">
-        <v>6992824</v>
+        <v>6992800</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348718</v>
+        <v>120348713</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558397</v>
+        <v>558254</v>
       </c>
       <c r="R30" t="n">
-        <v>6992950</v>
+        <v>6992648</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348730</v>
+        <v>120348723</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558182</v>
+        <v>558226</v>
       </c>
       <c r="R31" t="n">
-        <v>6992774</v>
+        <v>6992680</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348737</v>
+        <v>120348731</v>
       </c>
       <c r="B2" t="n">
         <v>79623</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558163</v>
+        <v>558175</v>
       </c>
       <c r="R2" t="n">
-        <v>6992824</v>
+        <v>6992771</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348728</v>
+        <v>120348721</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558195</v>
+        <v>558410</v>
       </c>
       <c r="R3" t="n">
-        <v>6992750</v>
+        <v>6992910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348718</v>
+        <v>120348717</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558397</v>
+        <v>558383</v>
       </c>
       <c r="R4" t="n">
-        <v>6992950</v>
+        <v>6992932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348731</v>
+        <v>120348735</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558175</v>
+        <v>558167</v>
       </c>
       <c r="R5" t="n">
-        <v>6992771</v>
+        <v>6992805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348739</v>
+        <v>120348726</v>
       </c>
       <c r="B6" t="n">
         <v>79623</v>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558156</v>
+        <v>558200</v>
       </c>
       <c r="R6" t="n">
-        <v>6992824</v>
+        <v>6992737</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348738</v>
+        <v>120348740</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558160</v>
+        <v>558150</v>
       </c>
       <c r="R7" t="n">
-        <v>6992833</v>
+        <v>6992821</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348740</v>
+        <v>120348718</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558150</v>
+        <v>558397</v>
       </c>
       <c r="R8" t="n">
-        <v>6992821</v>
+        <v>6992950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348721</v>
+        <v>120348713</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1434,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558410</v>
+        <v>558254</v>
       </c>
       <c r="R9" t="n">
-        <v>6992910</v>
+        <v>6992648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348725</v>
+        <v>120348733</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1648,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558215</v>
+        <v>558164</v>
       </c>
       <c r="R11" t="n">
-        <v>6992721</v>
+        <v>6992800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348729</v>
+        <v>120348719</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558183</v>
+        <v>558395</v>
       </c>
       <c r="R12" t="n">
-        <v>6992756</v>
+        <v>6992947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348736</v>
+        <v>120348742</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1839,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558159</v>
+        <v>558360</v>
       </c>
       <c r="R13" t="n">
-        <v>6992813</v>
+        <v>6992917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348722</v>
+        <v>120348729</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558400</v>
+        <v>558183</v>
       </c>
       <c r="R14" t="n">
-        <v>6992530</v>
+        <v>6992756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348742</v>
+        <v>120348725</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2145,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558360</v>
+        <v>558215</v>
       </c>
       <c r="R16" t="n">
-        <v>6992917</v>
+        <v>6992721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348745</v>
+        <v>120348744</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2247,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558319</v>
+        <v>558367</v>
       </c>
       <c r="R17" t="n">
-        <v>6992534</v>
+        <v>6992910</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348717</v>
+        <v>120348723</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558383</v>
+        <v>558226</v>
       </c>
       <c r="R18" t="n">
-        <v>6992932</v>
+        <v>6992680</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348735</v>
+        <v>120348720</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558167</v>
+        <v>558403</v>
       </c>
       <c r="R19" t="n">
-        <v>6992805</v>
+        <v>6992930</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2510,6 +2515,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,7 +2546,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348730</v>
+        <v>120348736</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -2576,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558182</v>
+        <v>558159</v>
       </c>
       <c r="R20" t="n">
-        <v>6992774</v>
+        <v>6992813</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,7 +2648,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348726</v>
+        <v>120348737</v>
       </c>
       <c r="B21" t="n">
         <v>79623</v>
@@ -2678,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558200</v>
+        <v>558163</v>
       </c>
       <c r="R21" t="n">
-        <v>6992737</v>
+        <v>6992824</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348716</v>
+        <v>120348739</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2766,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558377</v>
+        <v>558156</v>
       </c>
       <c r="R22" t="n">
-        <v>6992894</v>
+        <v>6992824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,11 +2826,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120348744</v>
+        <v>120348745</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2859,25 +2864,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558367</v>
+        <v>558319</v>
       </c>
       <c r="R23" t="n">
-        <v>6992910</v>
+        <v>6992534</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,7 +2954,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348741</v>
+        <v>120348730</v>
       </c>
       <c r="B24" t="n">
         <v>79623</v>
@@ -2989,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558382</v>
+        <v>558182</v>
       </c>
       <c r="R24" t="n">
-        <v>6992903</v>
+        <v>6992774</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348719</v>
+        <v>120348732</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558395</v>
+        <v>558177</v>
       </c>
       <c r="R25" t="n">
-        <v>6992947</v>
+        <v>6992782</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,11 +3132,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348714</v>
+        <v>120348741</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558187</v>
+        <v>558382</v>
       </c>
       <c r="R26" t="n">
-        <v>6992755</v>
+        <v>6992903</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,11 +3234,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3265,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120348732</v>
+        <v>120348722</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3281,21 +3276,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558177</v>
+        <v>558400</v>
       </c>
       <c r="R27" t="n">
-        <v>6992782</v>
+        <v>6992530</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,6 +3336,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3367,10 +3367,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348720</v>
+        <v>120348738</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558403</v>
+        <v>558160</v>
       </c>
       <c r="R28" t="n">
-        <v>6992930</v>
+        <v>6992833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,11 +3443,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3474,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348734</v>
+        <v>120348716</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,21 +3485,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558164</v>
+        <v>558377</v>
       </c>
       <c r="R29" t="n">
-        <v>6992800</v>
+        <v>6992894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,6 +3545,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,7 +3576,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348713</v>
+        <v>120348714</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558254</v>
+        <v>558187</v>
       </c>
       <c r="R30" t="n">
-        <v>6992648</v>
+        <v>6992755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348723</v>
+        <v>120348728</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558226</v>
+        <v>558195</v>
       </c>
       <c r="R31" t="n">
-        <v>6992680</v>
+        <v>6992750</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348733</v>
+        <v>120348719</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558164</v>
+        <v>558395</v>
       </c>
       <c r="R11" t="n">
-        <v>6992800</v>
+        <v>6992947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348719</v>
+        <v>120348733</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558395</v>
+        <v>558164</v>
       </c>
       <c r="R12" t="n">
-        <v>6992947</v>
+        <v>6992800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3367,10 +3367,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348738</v>
+        <v>120348716</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558160</v>
+        <v>558377</v>
       </c>
       <c r="R28" t="n">
-        <v>6992833</v>
+        <v>6992894</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,6 +3443,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3469,7 +3474,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348716</v>
+        <v>120348714</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558377</v>
+        <v>558187</v>
       </c>
       <c r="R29" t="n">
-        <v>6992894</v>
+        <v>6992755</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3576,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348714</v>
+        <v>120348738</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3592,21 +3597,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558187</v>
+        <v>558160</v>
       </c>
       <c r="R30" t="n">
-        <v>6992755</v>
+        <v>6992833</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,11 +3657,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348731</v>
+        <v>120348715</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558175</v>
+        <v>558347</v>
       </c>
       <c r="R2" t="n">
-        <v>6992771</v>
+        <v>6992956</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348721</v>
+        <v>120348739</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558410</v>
+        <v>558156</v>
       </c>
       <c r="R3" t="n">
-        <v>6992910</v>
+        <v>6992824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348717</v>
+        <v>120348732</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558383</v>
+        <v>558177</v>
       </c>
       <c r="R4" t="n">
-        <v>6992932</v>
+        <v>6992782</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348735</v>
+        <v>120348737</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558167</v>
+        <v>558163</v>
       </c>
       <c r="R5" t="n">
-        <v>6992805</v>
+        <v>6992824</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348740</v>
+        <v>120348742</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558150</v>
+        <v>558360</v>
       </c>
       <c r="R7" t="n">
-        <v>6992821</v>
+        <v>6992917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348718</v>
+        <v>120348716</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558397</v>
+        <v>558377</v>
       </c>
       <c r="R8" t="n">
-        <v>6992950</v>
+        <v>6992894</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348713</v>
+        <v>120348730</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558254</v>
+        <v>558182</v>
       </c>
       <c r="R9" t="n">
-        <v>6992648</v>
+        <v>6992774</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348715</v>
+        <v>120348728</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558347</v>
+        <v>558195</v>
       </c>
       <c r="R10" t="n">
-        <v>6992956</v>
+        <v>6992750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1577,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348719</v>
+        <v>120348729</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558395</v>
+        <v>558183</v>
       </c>
       <c r="R11" t="n">
-        <v>6992947</v>
+        <v>6992756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348733</v>
+        <v>120348719</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558164</v>
+        <v>558395</v>
       </c>
       <c r="R12" t="n">
-        <v>6992800</v>
+        <v>6992947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348742</v>
+        <v>120348745</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558360</v>
+        <v>558319</v>
       </c>
       <c r="R13" t="n">
-        <v>6992917</v>
+        <v>6992534</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348729</v>
+        <v>120348724</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -1969,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558183</v>
+        <v>558220</v>
       </c>
       <c r="R14" t="n">
-        <v>6992756</v>
+        <v>6992703</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348724</v>
+        <v>120348731</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2071,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558220</v>
+        <v>558175</v>
       </c>
       <c r="R15" t="n">
-        <v>6992703</v>
+        <v>6992771</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348725</v>
+        <v>120348744</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558215</v>
+        <v>558367</v>
       </c>
       <c r="R16" t="n">
-        <v>6992721</v>
+        <v>6992910</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348744</v>
+        <v>120348722</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558367</v>
+        <v>558400</v>
       </c>
       <c r="R17" t="n">
-        <v>6992910</v>
+        <v>6992530</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,6 +2296,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348723</v>
+        <v>120348713</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558226</v>
+        <v>558254</v>
       </c>
       <c r="R18" t="n">
-        <v>6992680</v>
+        <v>6992648</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348720</v>
+        <v>120348741</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558403</v>
+        <v>558382</v>
       </c>
       <c r="R19" t="n">
-        <v>6992930</v>
+        <v>6992903</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,11 +2510,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348736</v>
+        <v>120348733</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -2586,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558159</v>
+        <v>558164</v>
       </c>
       <c r="R20" t="n">
-        <v>6992813</v>
+        <v>6992800</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348737</v>
+        <v>120348718</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558163</v>
+        <v>558397</v>
       </c>
       <c r="R21" t="n">
-        <v>6992824</v>
+        <v>6992950</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,6 +2714,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348739</v>
+        <v>120348725</v>
       </c>
       <c r="B22" t="n">
         <v>79623</v>
@@ -2790,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558156</v>
+        <v>558215</v>
       </c>
       <c r="R22" t="n">
-        <v>6992824</v>
+        <v>6992721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120348745</v>
+        <v>120348736</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558319</v>
+        <v>558159</v>
       </c>
       <c r="R23" t="n">
-        <v>6992534</v>
+        <v>6992813</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,7 +2949,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348730</v>
+        <v>120348738</v>
       </c>
       <c r="B24" t="n">
         <v>79623</v>
@@ -2994,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558182</v>
+        <v>558160</v>
       </c>
       <c r="R24" t="n">
-        <v>6992774</v>
+        <v>6992833</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348732</v>
+        <v>120348720</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,21 +3067,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558177</v>
+        <v>558403</v>
       </c>
       <c r="R25" t="n">
-        <v>6992782</v>
+        <v>6992930</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348741</v>
+        <v>120348721</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558382</v>
+        <v>558410</v>
       </c>
       <c r="R26" t="n">
-        <v>6992903</v>
+        <v>6992910</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,6 +3234,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3260,7 +3265,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120348722</v>
+        <v>120348717</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3300,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558400</v>
+        <v>558383</v>
       </c>
       <c r="R27" t="n">
-        <v>6992530</v>
+        <v>6992932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,7 +3345,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3367,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348716</v>
+        <v>120348735</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,21 +3388,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558377</v>
+        <v>558167</v>
       </c>
       <c r="R28" t="n">
-        <v>6992894</v>
+        <v>6992805</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,11 +3448,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3474,10 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348714</v>
+        <v>120348723</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,21 +3490,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558187</v>
+        <v>558226</v>
       </c>
       <c r="R29" t="n">
-        <v>6992755</v>
+        <v>6992680</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,11 +3550,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3581,7 +3576,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348738</v>
+        <v>120348740</v>
       </c>
       <c r="B30" t="n">
         <v>79623</v>
@@ -3621,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558160</v>
+        <v>558150</v>
       </c>
       <c r="R30" t="n">
-        <v>6992833</v>
+        <v>6992821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3683,10 +3678,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348728</v>
+        <v>120348714</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,21 +3694,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3723,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558195</v>
+        <v>558187</v>
       </c>
       <c r="R31" t="n">
-        <v>6992750</v>
+        <v>6992755</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,6 +3754,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348715</v>
+        <v>120348734</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558347</v>
+        <v>558164</v>
       </c>
       <c r="R2" t="n">
-        <v>6992956</v>
+        <v>6992800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348739</v>
+        <v>120348730</v>
       </c>
       <c r="B3" t="n">
         <v>79623</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558156</v>
+        <v>558182</v>
       </c>
       <c r="R3" t="n">
-        <v>6992824</v>
+        <v>6992774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348732</v>
+        <v>120348736</v>
       </c>
       <c r="B4" t="n">
         <v>79623</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558177</v>
+        <v>558159</v>
       </c>
       <c r="R4" t="n">
-        <v>6992782</v>
+        <v>6992813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348737</v>
+        <v>120348738</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558163</v>
+        <v>558160</v>
       </c>
       <c r="R5" t="n">
-        <v>6992824</v>
+        <v>6992833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348726</v>
+        <v>120348729</v>
       </c>
       <c r="B6" t="n">
         <v>79623</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558200</v>
+        <v>558183</v>
       </c>
       <c r="R6" t="n">
-        <v>6992737</v>
+        <v>6992756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348742</v>
+        <v>120348719</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558360</v>
+        <v>558395</v>
       </c>
       <c r="R7" t="n">
-        <v>6992917</v>
+        <v>6992947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348716</v>
+        <v>120348721</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558377</v>
+        <v>558410</v>
       </c>
       <c r="R8" t="n">
-        <v>6992894</v>
+        <v>6992910</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348730</v>
+        <v>120348726</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558182</v>
+        <v>558200</v>
       </c>
       <c r="R9" t="n">
-        <v>6992774</v>
+        <v>6992737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348728</v>
+        <v>120348724</v>
       </c>
       <c r="B10" t="n">
         <v>79623</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558195</v>
+        <v>558220</v>
       </c>
       <c r="R10" t="n">
-        <v>6992750</v>
+        <v>6992703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348729</v>
+        <v>120348728</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558183</v>
+        <v>558195</v>
       </c>
       <c r="R11" t="n">
-        <v>6992756</v>
+        <v>6992750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348719</v>
+        <v>120348723</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558395</v>
+        <v>558226</v>
       </c>
       <c r="R12" t="n">
-        <v>6992947</v>
+        <v>6992680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348745</v>
+        <v>120348737</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558319</v>
+        <v>558163</v>
       </c>
       <c r="R13" t="n">
-        <v>6992534</v>
+        <v>6992824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348724</v>
+        <v>120348739</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558220</v>
+        <v>558156</v>
       </c>
       <c r="R14" t="n">
-        <v>6992703</v>
+        <v>6992824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348731</v>
+        <v>120348741</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558175</v>
+        <v>558382</v>
       </c>
       <c r="R15" t="n">
-        <v>6992771</v>
+        <v>6992903</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348744</v>
+        <v>120348731</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558367</v>
+        <v>558175</v>
       </c>
       <c r="R16" t="n">
-        <v>6992910</v>
+        <v>6992771</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348722</v>
+        <v>120348725</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558400</v>
+        <v>558215</v>
       </c>
       <c r="R17" t="n">
-        <v>6992530</v>
+        <v>6992721</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348713</v>
+        <v>120348718</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558254</v>
+        <v>558397</v>
       </c>
       <c r="R18" t="n">
-        <v>6992648</v>
+        <v>6992950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,7 +2397,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348741</v>
+        <v>120348714</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558382</v>
+        <v>558187</v>
       </c>
       <c r="R19" t="n">
-        <v>6992903</v>
+        <v>6992755</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2510,6 +2500,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348733</v>
+        <v>120348715</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558164</v>
+        <v>558347</v>
       </c>
       <c r="R20" t="n">
-        <v>6992800</v>
+        <v>6992956</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,6 +2607,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,7 +2638,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348718</v>
+        <v>120348716</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558397</v>
+        <v>558377</v>
       </c>
       <c r="R21" t="n">
-        <v>6992950</v>
+        <v>6992894</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348725</v>
+        <v>120348720</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558215</v>
+        <v>558403</v>
       </c>
       <c r="R22" t="n">
-        <v>6992721</v>
+        <v>6992930</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,7 +2852,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120348736</v>
+        <v>120348735</v>
       </c>
       <c r="B23" t="n">
         <v>79623</v>
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558159</v>
+        <v>558167</v>
       </c>
       <c r="R23" t="n">
-        <v>6992813</v>
+        <v>6992805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,7 +2954,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348738</v>
+        <v>120348732</v>
       </c>
       <c r="B24" t="n">
         <v>79623</v>
@@ -2989,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558160</v>
+        <v>558177</v>
       </c>
       <c r="R24" t="n">
-        <v>6992833</v>
+        <v>6992782</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348720</v>
+        <v>120348713</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558403</v>
+        <v>558254</v>
       </c>
       <c r="R25" t="n">
-        <v>6992930</v>
+        <v>6992648</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,7 +3136,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,7 +3163,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348721</v>
+        <v>120348717</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3198,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558410</v>
+        <v>558383</v>
       </c>
       <c r="R26" t="n">
-        <v>6992910</v>
+        <v>6992932</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,10 +3270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120348717</v>
+        <v>120348740</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3281,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558383</v>
+        <v>558150</v>
       </c>
       <c r="R27" t="n">
-        <v>6992932</v>
+        <v>6992821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,11 +3346,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348735</v>
+        <v>120348745</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3388,21 +3388,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558167</v>
+        <v>558319</v>
       </c>
       <c r="R28" t="n">
-        <v>6992805</v>
+        <v>6992534</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348723</v>
+        <v>120348722</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,21 +3490,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558226</v>
+        <v>558400</v>
       </c>
       <c r="R29" t="n">
-        <v>6992680</v>
+        <v>6992530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,6 +3550,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348740</v>
+        <v>120348742</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3588,25 +3593,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558150</v>
+        <v>558360</v>
       </c>
       <c r="R30" t="n">
-        <v>6992821</v>
+        <v>6992917</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348714</v>
+        <v>120348744</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3690,25 +3695,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558187</v>
+        <v>558367</v>
       </c>
       <c r="R31" t="n">
-        <v>6992755</v>
+        <v>6992910</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,11 +3759,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -3474,10 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348722</v>
+        <v>120348742</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3486,25 +3486,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558400</v>
+        <v>558360</v>
       </c>
       <c r="R29" t="n">
-        <v>6992530</v>
+        <v>6992917</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,11 +3550,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3581,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348742</v>
+        <v>120348722</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,25 +3588,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558360</v>
+        <v>558400</v>
       </c>
       <c r="R30" t="n">
-        <v>6992917</v>
+        <v>6992530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,6 +3652,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348736</v>
+        <v>120348723</v>
       </c>
       <c r="B2" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558159</v>
+        <v>558226</v>
       </c>
       <c r="R2" t="n">
-        <v>6992813</v>
+        <v>6992680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348726</v>
+        <v>120348724</v>
       </c>
       <c r="B3" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558200</v>
+        <v>558220</v>
       </c>
       <c r="R3" t="n">
-        <v>6992737</v>
+        <v>6992703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348721</v>
+        <v>120348725</v>
       </c>
       <c r="B4" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558410</v>
+        <v>558215</v>
       </c>
       <c r="R4" t="n">
-        <v>6992910</v>
+        <v>6992721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348717</v>
+        <v>120348726</v>
       </c>
       <c r="B5" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558383</v>
+        <v>558200</v>
       </c>
       <c r="R5" t="n">
-        <v>6992932</v>
+        <v>6992737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348730</v>
+        <v>120348728</v>
       </c>
       <c r="B6" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558182</v>
+        <v>558195</v>
       </c>
       <c r="R6" t="n">
-        <v>6992774</v>
+        <v>6992750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348734</v>
+        <v>120348729</v>
       </c>
       <c r="B7" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558164</v>
+        <v>558183</v>
       </c>
       <c r="R7" t="n">
-        <v>6992800</v>
+        <v>6992756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348723</v>
+        <v>120348730</v>
       </c>
       <c r="B8" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558226</v>
+        <v>558182</v>
       </c>
       <c r="R8" t="n">
-        <v>6992680</v>
+        <v>6992774</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348741</v>
+        <v>120348731</v>
       </c>
       <c r="B9" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558382</v>
+        <v>558175</v>
       </c>
       <c r="R9" t="n">
-        <v>6992903</v>
+        <v>6992771</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348728</v>
+        <v>120348732</v>
       </c>
       <c r="B10" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558195</v>
+        <v>558177</v>
       </c>
       <c r="R10" t="n">
-        <v>6992750</v>
+        <v>6992782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348740</v>
+        <v>120348733</v>
       </c>
       <c r="B11" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558150</v>
+        <v>558164</v>
       </c>
       <c r="R11" t="n">
-        <v>6992821</v>
+        <v>6992800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348724</v>
+        <v>120348735</v>
       </c>
       <c r="B12" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558220</v>
+        <v>558167</v>
       </c>
       <c r="R12" t="n">
-        <v>6992703</v>
+        <v>6992805</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348742</v>
+        <v>120348736</v>
       </c>
       <c r="B13" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558360</v>
+        <v>558159</v>
       </c>
       <c r="R13" t="n">
-        <v>6992917</v>
+        <v>6992813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348718</v>
+        <v>120348737</v>
       </c>
       <c r="B14" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558397</v>
+        <v>558163</v>
       </c>
       <c r="R14" t="n">
-        <v>6992950</v>
+        <v>6992824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348739</v>
+        <v>120348738</v>
       </c>
       <c r="B15" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558156</v>
+        <v>558160</v>
       </c>
       <c r="R15" t="n">
-        <v>6992824</v>
+        <v>6992833</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348735</v>
+        <v>120348739</v>
       </c>
       <c r="B16" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558167</v>
+        <v>558156</v>
       </c>
       <c r="R16" t="n">
-        <v>6992805</v>
+        <v>6992824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348719</v>
+        <v>120348740</v>
       </c>
       <c r="B17" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558395</v>
+        <v>558150</v>
       </c>
       <c r="R17" t="n">
-        <v>6992947</v>
+        <v>6992821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348737</v>
+        <v>120348741</v>
       </c>
       <c r="B18" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558163</v>
+        <v>558382</v>
       </c>
       <c r="R18" t="n">
-        <v>6992824</v>
+        <v>6992903</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348745</v>
+        <v>120348713</v>
       </c>
       <c r="B19" t="n">
-        <v>90656</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558319</v>
+        <v>558254</v>
       </c>
       <c r="R19" t="n">
-        <v>6992534</v>
+        <v>6992648</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2505,6 +2395,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,15 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348731</v>
+        <v>120348714</v>
       </c>
       <c r="B20" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558175</v>
+        <v>558187</v>
       </c>
       <c r="R20" t="n">
-        <v>6992771</v>
+        <v>6992755</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,15 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348725</v>
+        <v>120348715</v>
       </c>
       <c r="B21" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558215</v>
+        <v>558347</v>
       </c>
       <c r="R21" t="n">
-        <v>6992721</v>
+        <v>6992956</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,6 +2599,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,15 +2630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120348713</v>
+        <v>120348716</v>
       </c>
       <c r="B22" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558254</v>
+        <v>558377</v>
       </c>
       <c r="R22" t="n">
-        <v>6992648</v>
+        <v>6992894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2705,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,15 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120348720</v>
+        <v>120348717</v>
       </c>
       <c r="B23" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558403</v>
+        <v>558383</v>
       </c>
       <c r="R23" t="n">
-        <v>6992930</v>
+        <v>6992932</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,15 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120348716</v>
+        <v>120348718</v>
       </c>
       <c r="B24" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558377</v>
+        <v>558397</v>
       </c>
       <c r="R24" t="n">
-        <v>6992894</v>
+        <v>6992950</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,15 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120348732</v>
+        <v>120348719</v>
       </c>
       <c r="B25" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558177</v>
+        <v>558395</v>
       </c>
       <c r="R25" t="n">
-        <v>6992782</v>
+        <v>6992947</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,6 +3007,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,15 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120348714</v>
+        <v>120348720</v>
       </c>
       <c r="B26" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3198,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558187</v>
+        <v>558403</v>
       </c>
       <c r="R26" t="n">
-        <v>6992755</v>
+        <v>6992930</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,37 +3140,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120348744</v>
+        <v>120348721</v>
       </c>
       <c r="B27" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,7 +3175,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558367</v>
+        <v>558410</v>
       </c>
       <c r="R27" t="n">
         <v>6992910</v>
@@ -3341,6 +3211,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3367,15 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120348715</v>
+        <v>120348722</v>
       </c>
       <c r="B28" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558347</v>
+        <v>558400</v>
       </c>
       <c r="R28" t="n">
-        <v>6992956</v>
+        <v>6992530</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,7 +3317,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3474,37 +3344,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120348722</v>
+        <v>120348742</v>
       </c>
       <c r="B29" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3514,10 +3379,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558400</v>
+        <v>558360</v>
       </c>
       <c r="R29" t="n">
-        <v>6992530</v>
+        <v>6992917</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,11 +3415,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3581,37 +3441,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120348729</v>
+        <v>120348744</v>
       </c>
       <c r="B30" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558183</v>
+        <v>558367</v>
       </c>
       <c r="R30" t="n">
-        <v>6992756</v>
+        <v>6992910</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3683,53 +3538,55 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120348738</v>
+        <v>131293355</v>
       </c>
       <c r="B31" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103907</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>223284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnberget, Jmt</t>
+          <t>Fisksjötjärn, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558160</v>
+        <v>558183</v>
       </c>
       <c r="R31" t="n">
-        <v>6992833</v>
+        <v>6992753</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,14 +3608,24 @@
           <t>Håsjö</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>b162675c-6432-4b06-9674-7d693fef85b4</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stor gammal sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3773,15 +3640,491 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131293406</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fisksjötjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>558159</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6992825</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>34f148d1-7cb1-4f44-bcd0-074c3437ff11</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gammal naturlig sälg</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131293407</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fisksjötjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>558253</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6992569</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>529a9be6-9151-4fe8-ba99-83bab60ac774</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gammal ej hamlad sälg</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131293459</v>
+      </c>
+      <c r="B34" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fisksjötjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>558190</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6992662</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2b75173b-6b8f-4966-9eef-e1bb782d2e1e</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sälg 265 omkrets</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131293630</v>
+      </c>
+      <c r="B35" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fisksjötjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>558265</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6992568</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2172a752-913e-4019-9f8f-939fafb3299b</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Stor ej hamlad sälg</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28553-2024 artfynd.xlsx
+++ b/artfynd/A 28553-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348725</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348726</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348728</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348729</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348730</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348731</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348732</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348735</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348736</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348737</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348738</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348739</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348740</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348741</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348713</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348714</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348715</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348716</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348717</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348718</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348719</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3137,6 +3262,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348720</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3239,6 +3369,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348721</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3341,6 +3476,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348722</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3438,6 +3578,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348742</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3535,6 +3680,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348744</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3653,6 +3803,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293355</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3771,6 +3926,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293406</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3889,6 +4049,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293407</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4007,6 +4172,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293459</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4125,8 +4295,49 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>